--- a/IT23661974.xlsx
+++ b/IT23661974.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IT23661974\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_08B5D39BD50537C50420BF9C23B6E7735658C2DF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E0330D-4803-4BF5-8EFA-A5F0E72434F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="377">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -286,9 +286,6 @@
     <t>Repeated words</t>
   </si>
   <si>
-    <t>Evidence: Input begins with 'hari hari' (හරි හරි) - repeated word pattern. Tests system's ability to handle word repetition in chat-style Singlish.</t>
-  </si>
-  <si>
     <t>Rationale: No punctuation marks at the end of the sentence, which is common in casual chat-style conversation</t>
   </si>
   <si>
@@ -307,9 +304,6 @@
     <t>යමු යමු ඉක්මනට පෘන්තියට යන්න පරක්කු වෙනවා අපිට</t>
   </si>
   <si>
-    <t>Rationale: Sentence contains action ('yamu yamu'), time frame ('ikmanata'), destination ('puthiyata'), and consequence ('parakku wenawa') testing system's ability to parse complete thought structure</t>
-  </si>
-  <si>
     <t>Evidence: Input begins with 'yamu yamu' (යමු යමු - let's go let's go) - repeated word pattern for emphasis. Tests system's ability to handle word repetition in chat-style Singlish</t>
   </si>
   <si>
@@ -325,9 +319,6 @@
     <t>මචං... ඔයා ඉන්නවා ද??? මම එනවා... දැන්...</t>
   </si>
   <si>
-    <t>Evidence: Input contains multiple ellipses '...' (three times) and triple question marks '???'. Rationale: Non-standard punctuation confuses system</t>
-  </si>
-  <si>
     <t>Evidence: Input contains 'machan' - casual Sinhala slang. Rationale: Tests system's ability to handle informal/colloquial terms</t>
   </si>
   <si>
@@ -484,47 +475,689 @@
     <t>Neg_00021</t>
   </si>
   <si>
-    <t>mama yanwa</t>
-  </si>
-  <si>
-    <t>මම යනවා</t>
-  </si>
-  <si>
-    <t>PASS</t>
+    <t xml:space="preserve">oyg wifi pwd eka denna puluwanda mata </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ඔයාගේ wifi password එක දෙන්න පුළුවන්ද මට </t>
+  </si>
+  <si>
+    <t>ඔයාගේ wifi පව්ද ඒක දෙන්න පුළුවන්ද මට</t>
+  </si>
+  <si>
+    <t>English Digital Terms in Singlish</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'wifi' (wireless network term)</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to handle common digital/technology terminology in Singlish context</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'pwd' (standard abbreviation for password)</t>
   </si>
   <si>
     <t>Neg_00022</t>
   </si>
   <si>
+    <t>mata meke screenshort ekak aragena save karaganna on passe balanna</t>
+  </si>
+  <si>
+    <t>මට මේකේ screenshort එකක් අරගෙන save කරගන්න ඕනේ පස්සේ බලන්න</t>
+  </si>
+  <si>
+    <t>මට මේකේ screenshort එකක් අරගෙන save කරගන්න ඕං පස්සෙ බලන්න</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'screenshot' and 'save' - English digital/technology terms</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to handle digital terminology in Singlish context</t>
+  </si>
+  <si>
+    <t>Evidence: Two clauses - 'save karaganna on' (need to save) + 'passe balanna' (then look)</t>
+  </si>
+  <si>
     <t>Neg_00023</t>
   </si>
   <si>
+    <t>whatsapp eke group ekata api hdala join unnm wisthara denaganna puluwan</t>
+  </si>
+  <si>
+    <t>whatsapp එකේ group එකට අපි හදලා join උනානම් විස්තර දැනගන්න පුළුවන්</t>
+  </si>
+  <si>
+    <t>whatsapp එකේ group එකට අපි හදලා join උන්නම් විස්තර දැනගන්න පුළුවන්</t>
+  </si>
+  <si>
+    <t>Platform/App Names in Singlish</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'whatsapp' - popular messaging platform name</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to handle app names in Singlish context</t>
+  </si>
+  <si>
+    <t>Conditional sentences</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'group', 'join' - English digital/social media terms</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to handle English terminology mixed with Singlish</t>
+  </si>
+  <si>
     <t>Neg_00024</t>
   </si>
   <si>
+    <t>mama ada facebook eka blnkt  lassna post ekak dakka</t>
+  </si>
+  <si>
+    <t>මම අද facebook එක බලනකොට ලස්සන post එකක් දැක්කා</t>
+  </si>
+  <si>
+    <t>මම අද Facebook එක බලන්කට ලස්සන post එකක් දැක්කා</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'facebook' - popular social media platform name</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'post' - English social media term</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to handle English digital terminology mixed with Singlish</t>
+  </si>
+  <si>
     <t>Neg_00025</t>
   </si>
   <si>
+    <t>ASAP mek krnna. FYI mn dnnwa</t>
+  </si>
+  <si>
+    <t>ASAP මේක කරන්න. FYI මම දන්නවා</t>
+  </si>
+  <si>
+    <t>ASAP මේක කරන්න. FYI මන් දන්නවා</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'ASAP' (As Soon As Possible) and 'FYI' (For Your Information)</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to handle common English abbreviations in Singlish context</t>
+  </si>
+  <si>
     <t>Neg_00026</t>
   </si>
   <si>
+    <t>TBD tama dan PMSL kiyala mam dannawa ne</t>
+  </si>
+  <si>
+    <t>TBD තාම දැන් PMSL කියලා මම දන්නවා නේ</t>
+  </si>
+  <si>
+    <t>TBD තාම දැන් PMSL කියලා මම් දන්නවා නේ</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'TBD' (To Be Determined) and 'PMSL' (internet slang)</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to handle English abbreviations and internet slang in Singlish context</t>
+  </si>
+  <si>
+    <t>Evidence: 'tama' (තමයි), 'mam' (මම), 'ne' (නේ)</t>
+  </si>
+  <si>
     <t>Neg_00027</t>
   </si>
   <si>
+    <t>mata doc eka save karala email ekn ewnna on</t>
+  </si>
+  <si>
+    <t>මට doc එක save කරලා email එකන් එවන්න</t>
+  </si>
+  <si>
+    <t>මට doc එක save කරලා email එකන් එවන්න ඕනේ</t>
+  </si>
+  <si>
+    <t>English Clipped Forms</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'doc' (document), 'save', 'email' - English words shortened or used as-is in Singlish context</t>
+  </si>
+  <si>
+    <t>Evidence: 'ekn' (එකෙන්) - missing 'e', 'ewrnna' (එවන්න) - extra 'r' inserted</t>
+  </si>
+  <si>
     <t>Neg_00028</t>
   </si>
   <si>
+    <t>oya sub eka denna. mn info eka check karala dennam</t>
+  </si>
+  <si>
+    <t>ඔය sub එක දෙන්න. මම info එක check කරලා දෙන්නම්</t>
+  </si>
+  <si>
+    <t>ඔය sub එක දෙන්න. මන් info එක check කරලා දෙන්නම්</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'sub' (submission/subject) and 'info' (information) - common English clipped forms</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to handle shortened English words in Singlish context</t>
+  </si>
+  <si>
+    <t>Evidence: 'denna' (දෙන්න), 'karala' (කරලා), 'dennam' (දෙන්නම්)</t>
+  </si>
+  <si>
     <t>Neg_00029</t>
   </si>
   <si>
+    <t xml:space="preserve">api heta america yanwa  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">අපි හෙට America යනවා  </t>
+  </si>
+  <si>
+    <t>අපි හෙට අමෙරිකාව යනවා</t>
+  </si>
+  <si>
+    <t>Place Names Embedded in Singlish</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'america' - country name embedded in Singlish sentence</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to handle foreign place names without translation while maintaining Sinhala sentence structure</t>
+  </si>
+  <si>
+    <t>Evidence: 'api' (අපි), 'heta' (හෙට), 'yanawa' (යනවා)</t>
+  </si>
+  <si>
     <t>Neg_00030</t>
+  </si>
+  <si>
+    <t>api aniddata Kandy yanna inne dalada maligawa wadinna</t>
+  </si>
+  <si>
+    <t>අපි අනිද්දට kandy යන්න ඉන්නේ දළදා මාලිගාව වදින්න</t>
+  </si>
+  <si>
+    <t>අපි අනිද්දාට Kandy යන්න ඉන්නේ දළදා මාලිගාව වදින්න</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'Kandy' (city) and 'dalada maligawa' (Temple of the Tooth Relic)</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to handle local Sri Lankan place names and cultural sites in Singlish context</t>
+  </si>
+  <si>
+    <t>vidence: 'api' (අපි), 'aniddata' (අනිද්දට), 'yanna' (යන්න), 'inne' (ඉන්නේ), 'wadinna' (බලන්න)</t>
+  </si>
+  <si>
+    <t>Neg_00031</t>
+  </si>
+  <si>
+    <t>Dinu kiwwa ada flm ek blnna yamu kyla</t>
+  </si>
+  <si>
+    <t>දිනු කිව්වා අද film එකක් බලන්න යමු කියලා</t>
+  </si>
+  <si>
+    <t>දිනූ කිව්වා අද ෆ්ලෑම් එක බලන්න යමු කියලා</t>
+  </si>
+  <si>
+    <t>Person Names Embedded in Singlish</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'Dinu' - person name embedded in Singlish sentence</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to handle proper names without translation in Singlish context</t>
+  </si>
+  <si>
+    <t>Isolated English Word Insertions</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'film' - English loanword (movie). Tests system's ability to recognize common English words integrated into Singlish</t>
+  </si>
+  <si>
+    <t>Neg_00032</t>
+  </si>
+  <si>
+    <t>mamai mage ylwa vimukthi ada pdm krnna in hwst</t>
+  </si>
+  <si>
+    <t>මමයි මගේ යාළුවා විමුක්ති අද පාඩම් කරන්න ඉන්නේ හවසට</t>
+  </si>
+  <si>
+    <t>මමයි මගේ ඇහැල්වා විමුක්ති අද පාඩම් කරන්න ඉන් හවසට</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'vimukthi' - Sinhala person name embedded in Singlish sentence</t>
+  </si>
+  <si>
+    <t>Evidence: 'ylwa' (yaluwa), 'krnna' (karanna), 'in' (inne), 'hwst' (hawasata)</t>
+  </si>
+  <si>
+    <t>Neg_00033</t>
+  </si>
+  <si>
+    <t>balanna pg 80 wisthara deela athi oya e tika kiyawala balanna</t>
+  </si>
+  <si>
+    <t>බලන්න page 80 විස්තර දීලා අති ඔයා ඒ ටික කියවලා බලන්න</t>
+  </si>
+  <si>
+    <t>බලන්න පෑග් 80 විස්තර දීලා අති ඔයා ඒ ටික කියවලා බලන්න</t>
+  </si>
+  <si>
+    <t>Inputs with Numbers</t>
+  </si>
+  <si>
+    <t>Evidence: Contains number '80' as page reference</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to recognize and handle page numbers in instructional context</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'pg' (page) - common English abbreviation</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to recognize standard English abbreviations mixed with Singlish</t>
+  </si>
+  <si>
+    <t>Neg_00034</t>
+  </si>
+  <si>
+    <t>ada thiyana mv eka price eka 1000yi neda?</t>
+  </si>
+  <si>
+    <t>අද තියන movie එක price එක 1000යි නේද?</t>
+  </si>
+  <si>
+    <t>අද තියන ම්ව් එක price එක 1000යි නේද?</t>
+  </si>
+  <si>
+    <t>Evidence: Contains '1000yi' - number with Sinhala suffix 'yi' (යි) indicating 'is/costs 1000'</t>
+  </si>
+  <si>
+    <t>Inputs with Currency</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'price eka' - English currency/value term 'price' with Sinhala article 'eka'. Tests system's ability to handle mixed English-Sinhala currency expressions</t>
+  </si>
+  <si>
+    <t>Neg_00035</t>
+  </si>
+  <si>
+    <t>oyata puluwanda mata dollar 200k denna</t>
+  </si>
+  <si>
+    <t>ඔයාට පුළුවන්ද මට ඩොලර් 200000ක් දෙන්න</t>
+  </si>
+  <si>
+    <t>ඔයාට පුලුවන්ද මට dollar 200ක් දෙන්න</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'dollar' - English currency unit</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to handle foreign currency terms in Singlish request contexts</t>
+  </si>
+  <si>
+    <t>Evidence: 'oyata' (ඔයාට), 'puluwanda' (පුළුවන්ද), 'mata' (මට), 'denna' (දෙන්න) - all standard romanizations</t>
+  </si>
+  <si>
+    <t>Neg_00036</t>
+  </si>
+  <si>
+    <t>Rs. 2,500 wage wenne</t>
+  </si>
+  <si>
+    <t>රු. 2,500 වගේ වෙන්නේ</t>
+  </si>
+  <si>
+    <t>Rs. 2,500 වගේ වෙන්නේ</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to recognize local currency symbols in Singlish statements</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to recognize standard Singlish romanization for comparison words and stative verbs</t>
+  </si>
+  <si>
+    <t>Neg_00037</t>
+  </si>
+  <si>
+    <t>7.45pmta enna mama innawa oya ekn</t>
+  </si>
+  <si>
+    <t>7.45pmට එන්න මම ඉන්නවා ඔයා එනකන්</t>
+  </si>
+  <si>
+    <t>7.45pmට එන්න මම ඉන්නවා ඔය එකෙන්</t>
+  </si>
+  <si>
+    <t>Inputs with Time Formats</t>
+  </si>
+  <si>
+    <t>Evidence: Contains '7.45pmta' - time '7.45pm' with Sinhala suffix 'ta'</t>
+  </si>
+  <si>
+    <t>Command form</t>
+  </si>
+  <si>
+    <t>Evidence: 'enna' (එන්න - come) is a direct command</t>
+  </si>
+  <si>
+    <t>Neg_00038</t>
+  </si>
+  <si>
+    <t>class eka 09.30am walata patan ganna. oya enawa da?</t>
+  </si>
+  <si>
+    <t>class එක 09.30am වලට පටන් ගන්න. ඔයා එනවා ද?</t>
+  </si>
+  <si>
+    <t>class එක 09.30ම් වලට පටන් ගන්න. ඔයා එනවා ද?</t>
+  </si>
+  <si>
+    <t>Evidence: Contains '09.30am walata' - time with period separator and Sinhala suffix 'walata'</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to handle chat-style time formats ('.' instead of ':') with temporal suffixes</t>
+  </si>
+  <si>
+    <t>Evidence: 'enawa da?' with 'da' question particle and '?' at end</t>
+  </si>
+  <si>
+    <t>Neg_00039</t>
+  </si>
+  <si>
+    <t>March 05 submisson eke last date eka neda?</t>
+  </si>
+  <si>
+    <t>March 05 submisson එකේ last date එක නේද?</t>
+  </si>
+  <si>
+    <t>මාර්තු 05 submisson එකේ last date එක නේද?</t>
+  </si>
+  <si>
+    <t>Inputs with Dates</t>
+  </si>
+  <si>
+    <t>Rationale: 'March 05' tests system's ability to handle month+day date formats (no year specified)</t>
+  </si>
+  <si>
+    <t>Evidence: Input contains date 'March 05' (month + day format). Contains English words 'submission', 'last date'. Contains romanization variants - 'eke' (එකේ - of the), 'eka' (එක - the), 'neda?' (නේද? - isn't it? question tag). Question mark '?' at the end</t>
+  </si>
+  <si>
+    <t>Neg_00040</t>
+  </si>
+  <si>
+    <t>2026/03/05 api trip ekak ynw oylt enwda ynn apit ekk</t>
+  </si>
+  <si>
+    <t>2026/03/05 අපි trip එකක් යනවා ඔයාලත් එනවද යන්න අපිත් එක්ක</t>
+  </si>
+  <si>
+    <t>2026/03/05 අපි trip එකක් යනවා ඔයාලට එනවද යන්න අපිට එකක්</t>
+  </si>
+  <si>
+    <t>Evidence: Input contains date '2026/03/05' (YYYY/MM/DD format). Contains English word 'trip'. Contains extreme romanization variants - 'ekak' → 'ek' (missing 'ak'), 'yanawa' → 'ynw' (vowels removed), 'oyalath' → 'oylt' (missing 'a', 'th')</t>
+  </si>
+  <si>
+    <t>ationale: '2026/03/05' tests system's ability to handle YYYY/MM/DD date format</t>
+  </si>
+  <si>
+    <t>Rationale: Extreme shortening tests vowel/consonant omission across multiple word types</t>
+  </si>
+  <si>
+    <t>Neg_00041</t>
+  </si>
+  <si>
+    <t>thawa km 15 withara yanna thiyanwa hotel eka lagata</t>
+  </si>
+  <si>
+    <t>තව කිලෝමිටර 15 විතර යන්න තියන්ව හොටෙල් එක ලගට</t>
+  </si>
+  <si>
+    <t>තව කිම් 15 විතර යන්න තියන්ව හොටෙල් එක ලගට</t>
+  </si>
+  <si>
+    <t>Inputs with Units of Measurements</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'km' - standard abbreviation for kilometers</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to recognize common measurement unit abbreviations in distance contexts</t>
+  </si>
+  <si>
+    <t>Evidence: Contains number '15' combined with 'km' unit</t>
+  </si>
+  <si>
+    <t>Neg_00042</t>
+  </si>
+  <si>
+    <t>ada party ekata mn cake kg 2.5k dennam</t>
+  </si>
+  <si>
+    <t>අද party එකට මම cake kg 2.5ක් දෙන්නම්</t>
+  </si>
+  <si>
+    <t>අද party එකට මන් cake kg 2.5ක් දෙන්නම්</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'kg' - standard abbreviation for kilograms</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to recognize measurement unit abbreviations in quantity contexts</t>
+  </si>
+  <si>
+    <t>Evidence: 'ada' (අද), 'ekata' (එකට), 'mn' (මම - shortened), 'dennam' (දෙන්නම්)</t>
+  </si>
+  <si>
+    <t>Neg_00043</t>
+  </si>
+  <si>
+    <t>machan ekak hari. api yamu bung. mama dannawa</t>
+  </si>
+  <si>
+    <t>මචන් එකක් හරි. අපි යමු බං. මම දන්නවා</t>
+  </si>
+  <si>
+    <t>මචං එකක් හරි. අපි යමු බුන්ග්. මම දන්නවා</t>
+  </si>
+  <si>
+    <t>Evidence: Contains slang 'machan', 'bung'.</t>
+  </si>
+  <si>
+    <t>Romanization 'ekak', 'hari', 'api', 'yamu', 'mama', 'dannawa'. Periods '.' separating three clauses</t>
+  </si>
+  <si>
+    <t>Neg_00044</t>
+  </si>
+  <si>
+    <t>ai mcho mama dannwa ne eka loku wadak nemei bng</t>
+  </si>
+  <si>
+    <t>ඇයි මචෝ මම දන්නවා නේ ඒක ලොකු වැඩක් නෙමෙයි බං</t>
+  </si>
+  <si>
+    <t>ඇයි මචෝ මම දන්නවා නේ ඒක ලොකු වැඩක් නෙමෙයි බන්ග්</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'ai' (exclamation), 'mcho' (casual address), 'ne' (confirmation particle), 'bng' (casual final particle)</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to recognize multiple types of casual conversation markers</t>
+  </si>
+  <si>
+    <t>Evidence: 'ai', 'mcho', 'mama', 'dannwa', 'eka', 'loku', 'wadak', 'nemei', 'bng' - standard and shortened romanizations</t>
+  </si>
+  <si>
+    <t>Neg_00045</t>
+  </si>
+  <si>
+    <t>link eka email eken evanna @kasun sir oya meka balanna</t>
+  </si>
+  <si>
+    <t>link එක email එකෙන් එවන්න @kasun sir ඔයා මේක බලන්න</t>
+  </si>
+  <si>
+    <t>link එක email එකෙන් එවන්න @කසුන් sir ඔයා මේක බලන්න</t>
+  </si>
+  <si>
+    <t>Online Identifiers in Singlish</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to recognize and handle social media/chat-style mentions</t>
+  </si>
+  <si>
+    <t>Neg_00046</t>
+  </si>
+  <si>
+    <t>menna me link ekn https://cweb.sliit.lk cw ekt join wl blnn</t>
+  </si>
+  <si>
+    <t>මෙන්න මේ link එකෙන් https://courseweb.sliit.lk courseweb එකට join වෙලා බලන්න</t>
+  </si>
+  <si>
+    <t>මෙන්න මේ link එකන් https://cweb.sliit.lk CV එකට join වල බලන්න</t>
+  </si>
+  <si>
+    <t>Evidence: Contains URL 'https://cweb.sliit.lk' (shortened CourseWeb URL) and 'cw' (courseweb abbreviation)</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to handle real web addresses and platform abbreviations with Sinhala instructions</t>
+  </si>
+  <si>
+    <t>Evidence: 'cw' - abbreviation for 'courseweb'</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to recognize common platform abbreviations in online learning contexts</t>
+  </si>
+  <si>
+    <t>Neg_00047</t>
+  </si>
+  <si>
+    <t>mama inawa 🙂 oya enawa da? naththam yanna parakku wai</t>
+  </si>
+  <si>
+    <t>මම ඉන්නවා 🙂 ඔයා එනවා ද? නැත්තම් යන්න පරක්කු වෙයි</t>
+  </si>
+  <si>
+    <t>මම ඉනවා 🙂 ඔයා එනවා ද? නැත්තම් යන්න පරක්කු වෙයි</t>
+  </si>
+  <si>
+    <t>Inputs with Emojis</t>
+  </si>
+  <si>
+    <t>Evidence: Contains '😊' (smiling face emoji) in sentence</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to recognize and preserve emoji positioning in transliteration</t>
+  </si>
+  <si>
+    <t>Evidence: 'oya enawa da?' - yes/no question with 'da' particle and '?'</t>
+  </si>
+  <si>
+    <t>Neg_00048</t>
+  </si>
+  <si>
+    <t>ayyo api danawa ne 😞 oya innawa thanata api ennam 😊</t>
+  </si>
+  <si>
+    <t>අය්යෝ අපි දන්නවා නේ 😞 ඔයා ඉන්නවා තැනට අපි එන්නම් 😊</t>
+  </si>
+  <si>
+    <t>අය්යෝ අපි දානවා නේ 😞 ඔයා ඉන්නවා තැනට අපි එන්නම් 😊</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'ayyo' (අයියෝ - oh dear) exclamation, 'ne' (නේ - right?) confirmation particle</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to recognize casual expressions and conversation markers</t>
+  </si>
+  <si>
+    <t>Neg_00049</t>
+  </si>
+  <si>
+    <t>balamu balamu api ikmata me tika iwara kara ganna on</t>
+  </si>
+  <si>
+    <t>බලමු බලමු අපි ඉක්මට මේ ටික ඉවර කර ගන්න ඕනේ</t>
+  </si>
+  <si>
+    <t>බලමු බලමු අපි ඉක්මට මේ ටික ඉවර කර ගන්න ඕං</t>
+  </si>
+  <si>
+    <t>Neg_00050</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>me thiyana okkoma wada tika api thawal kal danne nathuwa hta udm api wada karanna on  nathm api passe parakku wenawa. mama dannawa oya dan innawan ne, but oya enna one. mokada mama oya balan inawan. api ekata yamu, api wada karamu, api eka finish karamu. passe api wena wada kranna one. mama dan krnnam meka.</t>
+  </si>
+  <si>
+    <t>මේ තියෙන ඔක්කොම වැඩ ටික අපි තව කල් දැන්නේ නැතුව හෙට උදේම අපි වැඩ කරන්න ඕනි, නැත්තම් අපි පස්සෙ පරක්කු වෙනවා. මම දන්නවා ඔයා දැන් ඉන්නවා නේ, but ඔයා එන්න ඕනි. මොකද මම ඔයා බලාගෙන ඉන්නවා. අපි එකට යමු, අපි වැඩ කරමු, අපි ඒක finish කරමු. පස්සෙ අපි වෙනත් වැඩ කරන්න ඕනි. මම දැන් කරන්නම් මේක.</t>
+  </si>
+  <si>
+    <t>මේ තියන ඔක්කොම වැඩ ටික අපි තවල් කල් දාන්නේ නැතුව හ්ට උද්ම් අපි වැඩ කරන්න ඕං නැත්නම් අපි පස්සේ පරක්කු වෙනවා. මම දන්නවා ඔයා දැන් ඉන්නවාන් නේ, but ඔයා එන්න ඕනේ. මොකද මම ඔය බලන් ඉනවන්. අපි එකට යමු, අපි වැඩ කරමු, අපි එක finish කරමු. පස්සේ අපි වෙන වැඩ කරන්න ඕනේ. මම දැන් කරන්නම් මේක.</t>
+  </si>
+  <si>
+    <t>Evidence: Contains English words 'but' and 'finish'</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to handle English transitions ('but') and action verbs ('finish') in Sinhala chat context</t>
+  </si>
+  <si>
+    <t>Evidence: 'but' (transition), 'finish' (action verb)</t>
+  </si>
+  <si>
+    <t>Evidence: Input begins with 'hari hari' (හරි හරි)  - repeated word pattern. Tests system's ability to handle word repetition in chat-style Singlish.</t>
+  </si>
+  <si>
+    <t>Rationale: Sentence contains action ('yamu yamu'), time frame ('ikmanata'), destination ('puthiyata') and consequence ('parakku wenawa') testing system's ability to parse complete thought structure</t>
+  </si>
+  <si>
+    <t>Evidence: Input contains multiple ellipses '...' (three times) and triple question marks '???'. Rationale: Non - standard punctuation confuses system</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's tolerance for extreme shortening, vowel omission and non - standard vowel replacements</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rationale: Tests system's tolerance for romanization variants and Sinhala sentence - final particles</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to handle common English clipped forms in mixed - language requests</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to handle Sinhala proper names without translation in chat - style context</t>
+  </si>
+  <si>
+    <t>Evidence: Contains 'Rs.'  standard Sri Lankan Rupee abbreviation</t>
+  </si>
+  <si>
+    <t>Rationale: Tests system's ability to handle period - separated time formats with Sinhala locative suffixes indicating 'at'</t>
+  </si>
+  <si>
+    <t>Rationale: 'submission', 'last date' are English academic/administrative terms. Tests system's ability to handle English terminology in deadline - related questions</t>
+  </si>
+  <si>
+    <t>Evidence: Contains '@kasun sir' - online mention/handle format with @ symbol, username 'kasun' and title 'sir'</t>
+  </si>
+  <si>
+    <t>Evidence: Input begins with 'hari hari' (බලමු බලමු) - repeated word pattern. Tests system's ability to handle word repetition in chat - style Singlish.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -563,6 +1196,18 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFF9FAFB"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFF9FAFB"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -572,7 +1217,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -619,11 +1264,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -632,6 +1288,13 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -651,6 +1314,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -931,7 +1612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:I206"/>
   <sheetFormatPr defaultRowHeight="49.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" customWidth="1"/>
@@ -970,22 +1651,22 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G2" s="2" t="s">
@@ -996,52 +1677,52 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -1052,12 +1733,12 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
       <c r="G7" s="2" t="s">
         <v>22</v>
       </c>
@@ -1066,42 +1747,42 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="2" t="s">
@@ -1112,52 +1793,52 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G14" s="2" t="s">
@@ -1168,12 +1849,12 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
       <c r="G15" s="2" t="s">
         <v>35</v>
       </c>
@@ -1182,44 +1863,44 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
       <c r="G16" s="2" t="s">
         <v>37</v>
       </c>
       <c r="H16" s="2"/>
     </row>
     <row r="17" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
     <row r="18" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G18" s="2" t="s">
@@ -1230,12 +1911,12 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
       <c r="G19" s="2" t="s">
         <v>44</v>
       </c>
@@ -1244,44 +1925,44 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
       <c r="G20" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H20" s="2"/>
     </row>
     <row r="21" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
     <row r="22" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G22" s="2" t="s">
@@ -1292,12 +1973,12 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
       <c r="G23" s="2" t="s">
         <v>52</v>
       </c>
@@ -1306,44 +1987,44 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
       <c r="G24" s="2" t="s">
         <v>54</v>
       </c>
       <c r="H24" s="2"/>
     </row>
     <row r="25" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
     </row>
     <row r="26" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G26" s="2" t="s">
@@ -1354,12 +2035,12 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
       <c r="G27" s="2" t="s">
         <v>46</v>
       </c>
@@ -1368,42 +2049,42 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
     <row r="29" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
     <row r="30" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G30" s="2" t="s">
@@ -1414,12 +2095,12 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
       <c r="G31" s="2" t="s">
         <v>52</v>
       </c>
@@ -1428,12 +2109,12 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
       <c r="G32" s="2" t="s">
         <v>46</v>
       </c>
@@ -1442,32 +2123,32 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
     </row>
     <row r="34" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G34" s="2" t="s">
@@ -1478,52 +2159,52 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
     </row>
     <row r="36" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
     </row>
     <row r="37" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
     </row>
     <row r="38" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="9" t="s">
+      <c r="A38" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G38" s="2" t="s">
@@ -1534,12 +2215,12 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="5"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
       <c r="G39" s="2" t="s">
         <v>46</v>
       </c>
@@ -1548,1023 +2229,2591 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
     </row>
     <row r="42" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>87</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>88</v>
+        <v>365</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
       <c r="G43" s="2" t="s">
         <v>54</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="5"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
+      <c r="A44" s="8"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
       <c r="G44" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
+      <c r="A45" s="9"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
     </row>
     <row r="46" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="9" t="s">
+      <c r="A46" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C46" s="4" t="s">
+      <c r="D46" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="E46" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="E46" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F46" s="7" t="s">
+      <c r="F46" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>87</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>95</v>
+        <v>366</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="5"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
+      <c r="A47" s="8"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
       <c r="G47" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="5"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
       <c r="G48" s="2" t="s">
         <v>54</v>
       </c>
       <c r="H48" s="2"/>
     </row>
     <row r="49" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
+      <c r="A49" s="9"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
     </row>
     <row r="50" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D50" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C50" s="4" t="s">
+      <c r="E50" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="D50" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="F50" s="7" t="s">
+      <c r="F50" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>101</v>
+        <v>367</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="5"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
+      <c r="A51" s="8"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
       <c r="G51" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="5"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
+      <c r="A52" s="8"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
       <c r="G52" s="2" t="s">
         <v>54</v>
       </c>
       <c r="H52" s="2"/>
     </row>
     <row r="53" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
+      <c r="A53" s="9"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
       <c r="G53" s="2" t="s">
         <v>52</v>
       </c>
       <c r="H53" s="2"/>
     </row>
     <row r="54" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="9" t="s">
+      <c r="A54" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E54" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="B54" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="F54" s="7" t="s">
+      <c r="F54" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="5"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
+      <c r="A55" s="8"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
       <c r="G55" s="2" t="s">
         <v>28</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="5"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
+      <c r="A56" s="8"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
     <row r="57" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
+      <c r="A57" s="9"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
     </row>
     <row r="58" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="9" t="s">
+      <c r="A58" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E58" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="B58" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="F58" s="7" t="s">
+      <c r="F58" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="5"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
+      <c r="A59" s="8"/>
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
       <c r="G59" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="5"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
+      <c r="A60" s="8"/>
+      <c r="B60" s="8"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
+      <c r="A61" s="9"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="9"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
     </row>
     <row r="62" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="9" t="s">
+      <c r="A62" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E62" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B62" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D62" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F62" s="7" t="s">
+      <c r="F62" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="5"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
+      <c r="A63" s="8"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="8"/>
       <c r="G63" s="2" t="s">
         <v>59</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="5"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
+      <c r="A64" s="8"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
+      <c r="A65" s="9"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
     </row>
     <row r="66" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="9" t="s">
+      <c r="A66" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E66" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="B66" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C66" s="4" t="s">
+      <c r="F66" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D66" s="10" t="s">
+      <c r="H66" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E66" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>127</v>
-      </c>
     </row>
     <row r="67" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="5"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
+      <c r="A67" s="8"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="8"/>
       <c r="G67" s="2" t="s">
         <v>54</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
+      <c r="A68" s="8"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="8"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
+      <c r="A69" s="9"/>
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="9"/>
+      <c r="F69" s="9"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
     <row r="70" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="9" t="s">
+      <c r="A70" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E70" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="B70" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C70" s="4" t="s">
+      <c r="F70" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D70" s="10" t="s">
+      <c r="H70" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E70" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="71" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
+      <c r="A71" s="8"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="8"/>
       <c r="G71" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="5"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
+      <c r="A72" s="8"/>
+      <c r="B72" s="8"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="8"/>
       <c r="G72" s="2" t="s">
         <v>54</v>
       </c>
       <c r="H72" s="2"/>
     </row>
     <row r="73" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="6"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="6"/>
+      <c r="A73" s="9"/>
+      <c r="B73" s="9"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9"/>
+      <c r="E73" s="9"/>
+      <c r="F73" s="9"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
     </row>
     <row r="74" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="9" t="s">
+      <c r="A74" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E74" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B74" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C74" s="4" t="s">
+      <c r="F74" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D74" s="10" t="s">
+      <c r="H74" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E74" s="8" t="s">
+    </row>
+    <row r="75" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="8"/>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+      <c r="G75" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F74" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G74" s="2" t="s">
+      <c r="H75" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="H74" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>144</v>
-      </c>
     </row>
     <row r="76" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="5"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
+      <c r="A76" s="8"/>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
       <c r="G76" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="6"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6"/>
+      <c r="A77" s="9"/>
+      <c r="B77" s="9"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="9"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D78" s="13" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="9" t="s">
+      <c r="E78" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B78" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C78" s="4" t="s">
+      <c r="F78" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H78" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D78" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>151</v>
-      </c>
     </row>
     <row r="79" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="5"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
+      <c r="A79" s="8"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
       <c r="G79" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="5"/>
-      <c r="B80" s="5"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="5"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="5"/>
+      <c r="A80" s="8"/>
+      <c r="B80" s="8"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="8"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="8"/>
       <c r="G80" s="2" t="s">
         <v>54</v>
       </c>
       <c r="H80" s="2"/>
     </row>
     <row r="81" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="6"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
+      <c r="A81" s="9"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="9"/>
+      <c r="F81" s="9"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
     </row>
     <row r="82" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="9" t="s">
+      <c r="A82" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B82" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D82" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="E82" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="F82" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="8"/>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="8"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="8"/>
+      <c r="G84" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="9"/>
+      <c r="B85" s="9"/>
+      <c r="C85" s="9"/>
+      <c r="D85" s="9"/>
+      <c r="E85" s="9"/>
+      <c r="F85" s="9"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+    </row>
+    <row r="86" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B86" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="E86" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="F86" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="8"/>
+      <c r="B87" s="8"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="8"/>
+      <c r="E87" s="8"/>
+      <c r="F87" s="8"/>
+      <c r="G87" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="8"/>
+      <c r="B88" s="8"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="8"/>
+      <c r="E88" s="8"/>
+      <c r="F88" s="8"/>
+      <c r="G88" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="9"/>
+      <c r="B89" s="9"/>
+      <c r="C89" s="9"/>
+      <c r="D89" s="9"/>
+      <c r="E89" s="9"/>
+      <c r="F89" s="9"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+    </row>
+    <row r="90" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="B90" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="E90" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="8"/>
+      <c r="B91" s="8"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="8"/>
+      <c r="F91" s="8"/>
+      <c r="G91" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="8"/>
+      <c r="B92" s="8"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="8"/>
+      <c r="E92" s="8"/>
+      <c r="F92" s="8"/>
+      <c r="G92" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="9"/>
+      <c r="B93" s="9"/>
+      <c r="C93" s="9"/>
+      <c r="D93" s="9"/>
+      <c r="E93" s="9"/>
+      <c r="F93" s="9"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B94" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="E94" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="F94" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="8"/>
+      <c r="B95" s="8"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="8"/>
+      <c r="E95" s="8"/>
+      <c r="F95" s="8"/>
+      <c r="G95" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="8"/>
+      <c r="B96" s="8"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="8"/>
+      <c r="E96" s="8"/>
+      <c r="F96" s="8"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="9"/>
+      <c r="B97" s="9"/>
+      <c r="C97" s="9"/>
+      <c r="D97" s="9"/>
+      <c r="E97" s="9"/>
+      <c r="F97" s="9"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+    </row>
+    <row r="98" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B98" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C82" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D82" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="5"/>
-      <c r="B83" s="5"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="5"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
-    </row>
-    <row r="84" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="5"/>
-      <c r="B84" s="5"/>
-      <c r="C84" s="5"/>
-      <c r="D84" s="5"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
-    </row>
-    <row r="85" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-    </row>
-    <row r="86" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="B86" s="7"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="10"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="7"/>
-    </row>
-    <row r="87" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="5"/>
-      <c r="B87" s="5"/>
-      <c r="C87" s="5"/>
-      <c r="D87" s="5"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
-    </row>
-    <row r="88" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="5"/>
-      <c r="B88" s="5"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="5"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
-    </row>
-    <row r="89" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="6"/>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
-    </row>
-    <row r="90" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="B90" s="7"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="10"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="7"/>
-    </row>
-    <row r="91" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="5"/>
-      <c r="B91" s="5"/>
-      <c r="C91" s="5"/>
-      <c r="D91" s="5"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="5"/>
-    </row>
-    <row r="92" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="5"/>
-      <c r="B92" s="5"/>
-      <c r="C92" s="5"/>
-      <c r="D92" s="5"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="5"/>
-    </row>
-    <row r="93" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="6"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="6"/>
-      <c r="D93" s="6"/>
-      <c r="E93" s="6"/>
-      <c r="F93" s="6"/>
-    </row>
-    <row r="94" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B94" s="7"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="10"/>
-      <c r="E94" s="8"/>
-      <c r="F94" s="7"/>
-    </row>
-    <row r="95" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="5"/>
-      <c r="B95" s="5"/>
-      <c r="C95" s="5"/>
-      <c r="D95" s="5"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
-    </row>
-    <row r="96" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="5"/>
-      <c r="B96" s="5"/>
-      <c r="C96" s="5"/>
-      <c r="D96" s="5"/>
-      <c r="E96" s="5"/>
-      <c r="F96" s="5"/>
-    </row>
-    <row r="97" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="6"/>
-      <c r="D97" s="6"/>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
-    </row>
-    <row r="98" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="B98" s="7"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="10"/>
-      <c r="E98" s="8"/>
-      <c r="F98" s="7"/>
-    </row>
-    <row r="99" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="5"/>
-      <c r="B99" s="5"/>
-      <c r="C99" s="5"/>
-      <c r="D99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5"/>
-    </row>
-    <row r="100" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="5"/>
-      <c r="B100" s="5"/>
-      <c r="C100" s="5"/>
-      <c r="D100" s="5"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="5"/>
-    </row>
-    <row r="101" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="6"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-    </row>
-    <row r="102" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="B102" s="7"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="10"/>
-      <c r="E102" s="8"/>
-      <c r="F102" s="7"/>
-    </row>
-    <row r="103" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="5"/>
-      <c r="B103" s="5"/>
-      <c r="C103" s="5"/>
-      <c r="D103" s="5"/>
-      <c r="E103" s="5"/>
-      <c r="F103" s="5"/>
-    </row>
-    <row r="104" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="5"/>
-      <c r="B104" s="5"/>
-      <c r="C104" s="5"/>
-      <c r="D104" s="5"/>
-      <c r="E104" s="5"/>
-      <c r="F104" s="5"/>
-    </row>
-    <row r="105" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6"/>
-      <c r="C105" s="6"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="6"/>
-      <c r="F105" s="6"/>
-    </row>
-    <row r="106" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="B106" s="7"/>
-      <c r="C106" s="4"/>
-      <c r="D106" s="10"/>
-      <c r="E106" s="8"/>
-      <c r="F106" s="7"/>
-    </row>
-    <row r="107" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="5"/>
-      <c r="B107" s="5"/>
-      <c r="C107" s="5"/>
-      <c r="D107" s="5"/>
-      <c r="E107" s="5"/>
-      <c r="F107" s="5"/>
-    </row>
-    <row r="108" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="5"/>
-      <c r="B108" s="5"/>
-      <c r="C108" s="5"/>
-      <c r="D108" s="5"/>
-      <c r="E108" s="5"/>
-      <c r="F108" s="5"/>
-    </row>
-    <row r="109" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="6"/>
-      <c r="B109" s="6"/>
-      <c r="C109" s="6"/>
-      <c r="D109" s="6"/>
-      <c r="E109" s="6"/>
-      <c r="F109" s="6"/>
-    </row>
-    <row r="110" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="B110" s="7"/>
-      <c r="C110" s="4"/>
-      <c r="D110" s="10"/>
-      <c r="E110" s="8"/>
-      <c r="F110" s="7"/>
-    </row>
-    <row r="111" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="5"/>
-      <c r="B111" s="5"/>
-      <c r="C111" s="5"/>
-      <c r="D111" s="5"/>
-      <c r="E111" s="5"/>
-      <c r="F111" s="5"/>
-    </row>
-    <row r="112" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="5"/>
-      <c r="B112" s="5"/>
-      <c r="C112" s="5"/>
-      <c r="D112" s="5"/>
-      <c r="E112" s="5"/>
-      <c r="F112" s="5"/>
-    </row>
-    <row r="113" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="6"/>
-      <c r="B113" s="6"/>
-      <c r="C113" s="6"/>
-      <c r="D113" s="6"/>
-      <c r="E113" s="6"/>
-      <c r="F113" s="6"/>
-    </row>
-    <row r="114" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="B114" s="7"/>
-      <c r="C114" s="4"/>
-      <c r="D114" s="10"/>
-      <c r="E114" s="8"/>
-      <c r="F114" s="7"/>
-    </row>
-    <row r="115" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="5"/>
-      <c r="B115" s="5"/>
-      <c r="C115" s="5"/>
-      <c r="D115" s="5"/>
-      <c r="E115" s="5"/>
-      <c r="F115" s="5"/>
-    </row>
-    <row r="116" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="5"/>
-      <c r="B116" s="5"/>
-      <c r="C116" s="5"/>
-      <c r="D116" s="5"/>
-      <c r="E116" s="5"/>
-      <c r="F116" s="5"/>
-    </row>
-    <row r="117" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="6"/>
-      <c r="B117" s="6"/>
-      <c r="C117" s="6"/>
-      <c r="D117" s="6"/>
-      <c r="E117" s="6"/>
-      <c r="F117" s="6"/>
-    </row>
-    <row r="118" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="B118" s="7"/>
-      <c r="C118" s="4"/>
-      <c r="D118" s="10"/>
-      <c r="E118" s="8"/>
-      <c r="F118" s="7"/>
-    </row>
-    <row r="119" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="5"/>
-      <c r="B119" s="5"/>
-      <c r="C119" s="5"/>
-      <c r="D119" s="5"/>
-      <c r="E119" s="5"/>
-      <c r="F119" s="5"/>
-    </row>
-    <row r="120" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="5"/>
-      <c r="B120" s="5"/>
-      <c r="C120" s="5"/>
-      <c r="D120" s="5"/>
-      <c r="E120" s="5"/>
-      <c r="F120" s="5"/>
-    </row>
-    <row r="121" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="6"/>
-      <c r="B121" s="6"/>
-      <c r="C121" s="6"/>
-      <c r="D121" s="6"/>
-      <c r="E121" s="6"/>
-      <c r="F121" s="6"/>
+      <c r="C98" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="E98" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="F98" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="8"/>
+      <c r="B99" s="8"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="8"/>
+      <c r="E99" s="8"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="8"/>
+      <c r="B100" s="8"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="8"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="9"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="9"/>
+      <c r="D101" s="9"/>
+      <c r="E101" s="9"/>
+      <c r="F101" s="9"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+    </row>
+    <row r="102" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B102" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D102" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="E102" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="F102" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="8"/>
+      <c r="B103" s="8"/>
+      <c r="C103" s="8"/>
+      <c r="D103" s="8"/>
+      <c r="E103" s="8"/>
+      <c r="F103" s="8"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="8"/>
+      <c r="B104" s="8"/>
+      <c r="C104" s="8"/>
+      <c r="D104" s="8"/>
+      <c r="E104" s="8"/>
+      <c r="F104" s="8"/>
+      <c r="G104" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="9"/>
+      <c r="B105" s="9"/>
+      <c r="C105" s="9"/>
+      <c r="D105" s="9"/>
+      <c r="E105" s="9"/>
+      <c r="F105" s="9"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="B106" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D106" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E106" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="F106" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="8"/>
+      <c r="B107" s="8"/>
+      <c r="C107" s="8"/>
+      <c r="D107" s="8"/>
+      <c r="E107" s="8"/>
+      <c r="F107" s="8"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="8"/>
+      <c r="B108" s="8"/>
+      <c r="C108" s="8"/>
+      <c r="D108" s="8"/>
+      <c r="E108" s="8"/>
+      <c r="F108" s="8"/>
+      <c r="G108" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="9"/>
+      <c r="B109" s="9"/>
+      <c r="C109" s="9"/>
+      <c r="D109" s="9"/>
+      <c r="E109" s="9"/>
+      <c r="F109" s="9"/>
+      <c r="G109" s="2"/>
+      <c r="H109" s="2"/>
+    </row>
+    <row r="110" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="B110" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D110" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="E110" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="F110" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="8"/>
+      <c r="B111" s="8"/>
+      <c r="C111" s="8"/>
+      <c r="D111" s="8"/>
+      <c r="E111" s="8"/>
+      <c r="F111" s="8"/>
+      <c r="G111" s="2"/>
+      <c r="H111" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="8"/>
+      <c r="B112" s="8"/>
+      <c r="C112" s="8"/>
+      <c r="D112" s="8"/>
+      <c r="E112" s="8"/>
+      <c r="F112" s="8"/>
+      <c r="G112" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="9"/>
+      <c r="B113" s="9"/>
+      <c r="C113" s="9"/>
+      <c r="D113" s="9"/>
+      <c r="E113" s="9"/>
+      <c r="F113" s="9"/>
+      <c r="G113" s="2"/>
+      <c r="H113" s="2"/>
+    </row>
+    <row r="114" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="B114" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="D114" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="E114" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="F114" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="8"/>
+      <c r="B115" s="8"/>
+      <c r="C115" s="8"/>
+      <c r="D115" s="8"/>
+      <c r="E115" s="8"/>
+      <c r="F115" s="8"/>
+      <c r="G115" s="2"/>
+      <c r="H115" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="8"/>
+      <c r="B116" s="8"/>
+      <c r="C116" s="8"/>
+      <c r="D116" s="8"/>
+      <c r="E116" s="8"/>
+      <c r="F116" s="8"/>
+      <c r="G116" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="9"/>
+      <c r="B117" s="9"/>
+      <c r="C117" s="9"/>
+      <c r="D117" s="9"/>
+      <c r="E117" s="9"/>
+      <c r="F117" s="9"/>
+      <c r="G117" s="2"/>
+      <c r="H117" s="2"/>
+    </row>
+    <row r="118" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="B118" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="D118" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="E118" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="F118" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="8"/>
+      <c r="B119" s="8"/>
+      <c r="C119" s="8"/>
+      <c r="D119" s="8"/>
+      <c r="E119" s="8"/>
+      <c r="F119" s="8"/>
+      <c r="G119" s="2"/>
+      <c r="H119" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="8"/>
+      <c r="B120" s="8"/>
+      <c r="C120" s="8"/>
+      <c r="D120" s="8"/>
+      <c r="E120" s="8"/>
+      <c r="F120" s="8"/>
+      <c r="G120" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="9"/>
+      <c r="B121" s="9"/>
+      <c r="C121" s="9"/>
+      <c r="D121" s="9"/>
+      <c r="E121" s="9"/>
+      <c r="F121" s="9"/>
+      <c r="G121" s="2"/>
+      <c r="H121" s="2"/>
+    </row>
+    <row r="122" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="B122" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D122" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="E122" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="F122" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="8"/>
+      <c r="B123" s="8"/>
+      <c r="C123" s="8"/>
+      <c r="D123" s="8"/>
+      <c r="E123" s="8"/>
+      <c r="F123" s="8"/>
+      <c r="G123" s="2"/>
+      <c r="H123" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="8"/>
+      <c r="B124" s="8"/>
+      <c r="C124" s="8"/>
+      <c r="D124" s="8"/>
+      <c r="E124" s="8"/>
+      <c r="F124" s="8"/>
+      <c r="G124" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="9"/>
+      <c r="B125" s="9"/>
+      <c r="C125" s="9"/>
+      <c r="D125" s="9"/>
+      <c r="E125" s="9"/>
+      <c r="F125" s="9"/>
+      <c r="G125" s="2"/>
+      <c r="H125" s="2"/>
+    </row>
+    <row r="126" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="B126" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="D126" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="E126" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="F126" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="8"/>
+      <c r="B127" s="8"/>
+      <c r="C127" s="8"/>
+      <c r="D127" s="8"/>
+      <c r="E127" s="8"/>
+      <c r="F127" s="8"/>
+      <c r="G127" s="2"/>
+      <c r="H127" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="8"/>
+      <c r="B128" s="8"/>
+      <c r="C128" s="8"/>
+      <c r="D128" s="8"/>
+      <c r="E128" s="8"/>
+      <c r="F128" s="8"/>
+      <c r="G128" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="9"/>
+      <c r="B129" s="9"/>
+      <c r="C129" s="9"/>
+      <c r="D129" s="9"/>
+      <c r="E129" s="9"/>
+      <c r="F129" s="9"/>
+      <c r="G129" s="2"/>
+      <c r="H129" s="2"/>
+    </row>
+    <row r="130" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B130" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D130" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="E130" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="F130" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="8"/>
+      <c r="B131" s="8"/>
+      <c r="C131" s="8"/>
+      <c r="D131" s="8"/>
+      <c r="E131" s="8"/>
+      <c r="F131" s="8"/>
+      <c r="G131" s="2"/>
+      <c r="H131" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="8"/>
+      <c r="B132" s="8"/>
+      <c r="C132" s="8"/>
+      <c r="D132" s="8"/>
+      <c r="E132" s="8"/>
+      <c r="F132" s="8"/>
+      <c r="G132" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="9"/>
+      <c r="B133" s="9"/>
+      <c r="C133" s="9"/>
+      <c r="D133" s="9"/>
+      <c r="E133" s="9"/>
+      <c r="F133" s="9"/>
+      <c r="G133" s="2"/>
+      <c r="H133" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="B134" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D134" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="E134" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="F134" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="8"/>
+      <c r="B135" s="8"/>
+      <c r="C135" s="8"/>
+      <c r="D135" s="8"/>
+      <c r="E135" s="8"/>
+      <c r="F135" s="8"/>
+      <c r="G135" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="8"/>
+      <c r="B136" s="8"/>
+      <c r="C136" s="8"/>
+      <c r="D136" s="8"/>
+      <c r="E136" s="8"/>
+      <c r="F136" s="8"/>
+      <c r="G136" s="4"/>
+      <c r="H136" s="2"/>
+    </row>
+    <row r="137" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="9"/>
+      <c r="B137" s="9"/>
+      <c r="C137" s="9"/>
+      <c r="D137" s="9"/>
+      <c r="E137" s="9"/>
+      <c r="F137" s="9"/>
+      <c r="G137" s="2"/>
+      <c r="H137" s="2"/>
+    </row>
+    <row r="138" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="B138" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="D138" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="E138" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="F138" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="8"/>
+      <c r="B139" s="8"/>
+      <c r="C139" s="8"/>
+      <c r="D139" s="8"/>
+      <c r="E139" s="8"/>
+      <c r="F139" s="8"/>
+      <c r="G139" s="2"/>
+      <c r="H139" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="8"/>
+      <c r="B140" s="8"/>
+      <c r="C140" s="8"/>
+      <c r="D140" s="8"/>
+      <c r="E140" s="8"/>
+      <c r="F140" s="8"/>
+      <c r="G140" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="9"/>
+      <c r="B141" s="9"/>
+      <c r="C141" s="9"/>
+      <c r="D141" s="9"/>
+      <c r="E141" s="9"/>
+      <c r="F141" s="9"/>
+      <c r="G141" s="2"/>
+      <c r="H141" s="2"/>
+    </row>
+    <row r="142" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="B142" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="D142" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="E142" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="F142" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="8"/>
+      <c r="B143" s="8"/>
+      <c r="C143" s="8"/>
+      <c r="D143" s="8"/>
+      <c r="E143" s="8"/>
+      <c r="F143" s="8"/>
+      <c r="G143" s="2"/>
+      <c r="H143" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="8"/>
+      <c r="B144" s="8"/>
+      <c r="C144" s="8"/>
+      <c r="D144" s="8"/>
+      <c r="E144" s="8"/>
+      <c r="F144" s="8"/>
+      <c r="G144" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="9"/>
+      <c r="B145" s="9"/>
+      <c r="C145" s="9"/>
+      <c r="D145" s="9"/>
+      <c r="E145" s="9"/>
+      <c r="F145" s="9"/>
+      <c r="G145" s="2"/>
+      <c r="H145" s="2"/>
+    </row>
+    <row r="146" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B146" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="D146" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="E146" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="F146" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="8"/>
+      <c r="B147" s="8"/>
+      <c r="C147" s="8"/>
+      <c r="D147" s="8"/>
+      <c r="E147" s="8"/>
+      <c r="F147" s="8"/>
+      <c r="G147" s="2"/>
+      <c r="H147" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="8"/>
+      <c r="B148" s="8"/>
+      <c r="C148" s="8"/>
+      <c r="D148" s="8"/>
+      <c r="E148" s="8"/>
+      <c r="F148" s="8"/>
+      <c r="G148" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="9"/>
+      <c r="B149" s="9"/>
+      <c r="C149" s="9"/>
+      <c r="D149" s="9"/>
+      <c r="E149" s="9"/>
+      <c r="F149" s="9"/>
+      <c r="G149" s="2"/>
+      <c r="H149" s="2"/>
+    </row>
+    <row r="150" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="B150" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D150" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="E150" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="F150" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="8"/>
+      <c r="B151" s="8"/>
+      <c r="C151" s="8"/>
+      <c r="D151" s="8"/>
+      <c r="E151" s="8"/>
+      <c r="F151" s="8"/>
+      <c r="G151" s="2"/>
+      <c r="H151" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="8"/>
+      <c r="B152" s="8"/>
+      <c r="C152" s="8"/>
+      <c r="D152" s="8"/>
+      <c r="E152" s="8"/>
+      <c r="F152" s="8"/>
+      <c r="G152" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="9"/>
+      <c r="B153" s="9"/>
+      <c r="C153" s="9"/>
+      <c r="D153" s="9"/>
+      <c r="E153" s="9"/>
+      <c r="F153" s="9"/>
+      <c r="G153" s="2"/>
+      <c r="H153" s="2"/>
+    </row>
+    <row r="154" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="B154" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D154" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="E154" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="F154" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="8"/>
+      <c r="B155" s="8"/>
+      <c r="C155" s="8"/>
+      <c r="D155" s="8"/>
+      <c r="E155" s="8"/>
+      <c r="F155" s="8"/>
+      <c r="G155" s="2"/>
+      <c r="H155" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="8"/>
+      <c r="B156" s="8"/>
+      <c r="C156" s="8"/>
+      <c r="D156" s="8"/>
+      <c r="E156" s="8"/>
+      <c r="F156" s="8"/>
+      <c r="G156" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="9"/>
+      <c r="B157" s="9"/>
+      <c r="C157" s="9"/>
+      <c r="D157" s="9"/>
+      <c r="E157" s="9"/>
+      <c r="F157" s="9"/>
+      <c r="G157" s="2"/>
+      <c r="H157" s="2"/>
+    </row>
+    <row r="158" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="B158" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="D158" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="E158" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="F158" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="8"/>
+      <c r="B159" s="8"/>
+      <c r="C159" s="8"/>
+      <c r="D159" s="8"/>
+      <c r="E159" s="8"/>
+      <c r="F159" s="8"/>
+      <c r="G159" s="2"/>
+      <c r="H159" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="8"/>
+      <c r="B160" s="8"/>
+      <c r="C160" s="8"/>
+      <c r="D160" s="8"/>
+      <c r="E160" s="8"/>
+      <c r="F160" s="8"/>
+      <c r="G160" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="9"/>
+      <c r="B161" s="9"/>
+      <c r="C161" s="9"/>
+      <c r="D161" s="9"/>
+      <c r="E161" s="9"/>
+      <c r="F161" s="9"/>
+      <c r="G161" s="2"/>
+      <c r="H161" s="2"/>
+    </row>
+    <row r="162" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="B162" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D162" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="E162" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="F162" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="8"/>
+      <c r="B163" s="8"/>
+      <c r="C163" s="8"/>
+      <c r="D163" s="8"/>
+      <c r="E163" s="8"/>
+      <c r="F163" s="8"/>
+      <c r="G163" s="2"/>
+      <c r="H163" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="8"/>
+      <c r="B164" s="8"/>
+      <c r="C164" s="8"/>
+      <c r="D164" s="8"/>
+      <c r="E164" s="8"/>
+      <c r="F164" s="8"/>
+      <c r="G164" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="9"/>
+      <c r="B165" s="9"/>
+      <c r="C165" s="9"/>
+      <c r="D165" s="9"/>
+      <c r="E165" s="9"/>
+      <c r="F165" s="9"/>
+      <c r="G165" s="2"/>
+      <c r="H165" s="2"/>
+    </row>
+    <row r="166" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="B166" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C166" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="D166" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="E166" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="F166" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="8"/>
+      <c r="B167" s="8"/>
+      <c r="C167" s="8"/>
+      <c r="D167" s="8"/>
+      <c r="E167" s="8"/>
+      <c r="F167" s="8"/>
+      <c r="G167" s="2"/>
+      <c r="H167" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="8"/>
+      <c r="B168" s="8"/>
+      <c r="C168" s="8"/>
+      <c r="D168" s="8"/>
+      <c r="E168" s="8"/>
+      <c r="F168" s="8"/>
+      <c r="G168" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="9"/>
+      <c r="B169" s="9"/>
+      <c r="C169" s="9"/>
+      <c r="D169" s="9"/>
+      <c r="E169" s="9"/>
+      <c r="F169" s="9"/>
+      <c r="G169" s="2"/>
+      <c r="H169" s="2"/>
+    </row>
+    <row r="170" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B170" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C170" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D170" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="E170" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="F170" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G170" s="5"/>
+      <c r="H170" s="2"/>
+    </row>
+    <row r="171" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="8"/>
+      <c r="B171" s="8"/>
+      <c r="C171" s="8"/>
+      <c r="D171" s="8"/>
+      <c r="E171" s="8"/>
+      <c r="F171" s="8"/>
+      <c r="G171" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="8"/>
+      <c r="B172" s="8"/>
+      <c r="C172" s="8"/>
+      <c r="D172" s="8"/>
+      <c r="E172" s="8"/>
+      <c r="F172" s="8"/>
+      <c r="G172" s="2"/>
+      <c r="H172" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="9"/>
+      <c r="B173" s="9"/>
+      <c r="C173" s="9"/>
+      <c r="D173" s="9"/>
+      <c r="E173" s="9"/>
+      <c r="F173" s="9"/>
+      <c r="G173" s="2"/>
+      <c r="H173" s="2"/>
+    </row>
+    <row r="174" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A174" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="B174" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="D174" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="E174" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="F174" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="8"/>
+      <c r="B175" s="8"/>
+      <c r="C175" s="8"/>
+      <c r="D175" s="8"/>
+      <c r="E175" s="8"/>
+      <c r="F175" s="8"/>
+      <c r="G175" s="2"/>
+      <c r="H175" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="8"/>
+      <c r="B176" s="8"/>
+      <c r="C176" s="8"/>
+      <c r="D176" s="8"/>
+      <c r="E176" s="8"/>
+      <c r="F176" s="8"/>
+      <c r="G176" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H176" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="9"/>
+      <c r="B177" s="9"/>
+      <c r="C177" s="9"/>
+      <c r="D177" s="9"/>
+      <c r="E177" s="9"/>
+      <c r="F177" s="9"/>
+      <c r="G177" s="2"/>
+      <c r="H177" s="2"/>
+    </row>
+    <row r="178" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="B178" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="D178" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="E178" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="F178" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="H178" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="8"/>
+      <c r="B179" s="8"/>
+      <c r="C179" s="8"/>
+      <c r="D179" s="8"/>
+      <c r="E179" s="8"/>
+      <c r="F179" s="8"/>
+      <c r="G179" s="2"/>
+      <c r="H179" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="8"/>
+      <c r="B180" s="8"/>
+      <c r="C180" s="8"/>
+      <c r="D180" s="8"/>
+      <c r="E180" s="8"/>
+      <c r="F180" s="8"/>
+      <c r="G180" s="2"/>
+      <c r="H180" s="2"/>
+    </row>
+    <row r="181" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="9"/>
+      <c r="B181" s="9"/>
+      <c r="C181" s="9"/>
+      <c r="D181" s="9"/>
+      <c r="E181" s="9"/>
+      <c r="F181" s="9"/>
+      <c r="G181" s="2"/>
+      <c r="H181" s="2"/>
+    </row>
+    <row r="182" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="B182" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C182" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="D182" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="E182" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="F182" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="8"/>
+      <c r="B183" s="8"/>
+      <c r="C183" s="8"/>
+      <c r="D183" s="8"/>
+      <c r="E183" s="8"/>
+      <c r="F183" s="8"/>
+      <c r="G183" s="2"/>
+      <c r="H183" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="8"/>
+      <c r="B184" s="8"/>
+      <c r="C184" s="8"/>
+      <c r="D184" s="8"/>
+      <c r="E184" s="8"/>
+      <c r="F184" s="8"/>
+      <c r="G184" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H184" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="9"/>
+      <c r="B185" s="9"/>
+      <c r="C185" s="9"/>
+      <c r="D185" s="9"/>
+      <c r="E185" s="9"/>
+      <c r="F185" s="9"/>
+      <c r="G185" s="2"/>
+      <c r="H185" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="B186" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C186" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="D186" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="E186" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="F186" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="H186" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="8"/>
+      <c r="B187" s="8"/>
+      <c r="C187" s="8"/>
+      <c r="D187" s="8"/>
+      <c r="E187" s="8"/>
+      <c r="F187" s="8"/>
+      <c r="G187" s="2"/>
+      <c r="H187" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="8"/>
+      <c r="B188" s="8"/>
+      <c r="C188" s="8"/>
+      <c r="D188" s="8"/>
+      <c r="E188" s="8"/>
+      <c r="F188" s="8"/>
+      <c r="G188" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H188" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="9"/>
+      <c r="B189" s="9"/>
+      <c r="C189" s="9"/>
+      <c r="D189" s="9"/>
+      <c r="E189" s="9"/>
+      <c r="F189" s="9"/>
+      <c r="G189" s="2"/>
+      <c r="H189" s="2"/>
+    </row>
+    <row r="190" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="B190" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="D190" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="E190" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="F190" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="H190" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="8"/>
+      <c r="B191" s="8"/>
+      <c r="C191" s="8"/>
+      <c r="D191" s="8"/>
+      <c r="E191" s="8"/>
+      <c r="F191" s="8"/>
+      <c r="G191" s="2"/>
+      <c r="H191" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="8"/>
+      <c r="B192" s="8"/>
+      <c r="C192" s="8"/>
+      <c r="D192" s="8"/>
+      <c r="E192" s="8"/>
+      <c r="F192" s="8"/>
+      <c r="G192" s="2"/>
+      <c r="H192" s="2"/>
+    </row>
+    <row r="193" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="9"/>
+      <c r="B193" s="9"/>
+      <c r="C193" s="9"/>
+      <c r="D193" s="9"/>
+      <c r="E193" s="9"/>
+      <c r="F193" s="9"/>
+      <c r="G193" s="2"/>
+      <c r="H193" s="2"/>
+    </row>
+    <row r="194" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="B194" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C194" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="D194" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="E194" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="F194" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H194" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="8"/>
+      <c r="B195" s="8"/>
+      <c r="C195" s="8"/>
+      <c r="D195" s="8"/>
+      <c r="E195" s="8"/>
+      <c r="F195" s="8"/>
+      <c r="G195" s="2"/>
+      <c r="H195" s="2"/>
+    </row>
+    <row r="196" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="8"/>
+      <c r="B196" s="8"/>
+      <c r="C196" s="8"/>
+      <c r="D196" s="8"/>
+      <c r="E196" s="8"/>
+      <c r="F196" s="8"/>
+      <c r="G196" s="2"/>
+      <c r="H196" s="2"/>
+    </row>
+    <row r="197" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="9"/>
+      <c r="B197" s="9"/>
+      <c r="C197" s="9"/>
+      <c r="D197" s="9"/>
+      <c r="E197" s="9"/>
+      <c r="F197" s="9"/>
+      <c r="G197" s="2"/>
+      <c r="H197" s="2"/>
+    </row>
+    <row r="198" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="B198" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="C198" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="D198" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="E198" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="F198" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H198" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="8"/>
+      <c r="B199" s="8"/>
+      <c r="C199" s="8"/>
+      <c r="D199" s="8"/>
+      <c r="E199" s="8"/>
+      <c r="F199" s="8"/>
+      <c r="G199" s="2"/>
+      <c r="H199" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="8"/>
+      <c r="B200" s="8"/>
+      <c r="C200" s="8"/>
+      <c r="D200" s="8"/>
+      <c r="E200" s="8"/>
+      <c r="F200" s="8"/>
+      <c r="G200" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H200" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="9"/>
+      <c r="B201" s="9"/>
+      <c r="C201" s="9"/>
+      <c r="D201" s="9"/>
+      <c r="E201" s="9"/>
+      <c r="F201" s="9"/>
+      <c r="G201" s="2"/>
+      <c r="H201" s="2"/>
+      <c r="I201" s="21"/>
+    </row>
+    <row r="202" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A202" s="19"/>
+      <c r="B202" s="16"/>
+      <c r="C202" s="17"/>
+      <c r="D202" s="14"/>
+      <c r="E202" s="18"/>
+      <c r="F202" s="16"/>
+      <c r="G202" s="6"/>
+      <c r="H202" s="6"/>
+      <c r="I202" s="21"/>
+    </row>
+    <row r="203" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A203" s="15"/>
+      <c r="B203" s="15"/>
+      <c r="C203" s="15"/>
+      <c r="D203" s="15"/>
+      <c r="E203" s="15"/>
+      <c r="F203" s="15"/>
+      <c r="G203" s="6"/>
+      <c r="H203" s="6"/>
+    </row>
+    <row r="204" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="15"/>
+      <c r="B204" s="15"/>
+      <c r="C204" s="15"/>
+      <c r="D204" s="15"/>
+      <c r="E204" s="15"/>
+      <c r="F204" s="15"/>
+      <c r="G204" s="6"/>
+      <c r="H204" s="6"/>
+    </row>
+    <row r="205" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="20"/>
+      <c r="B205" s="15"/>
+      <c r="C205" s="15"/>
+      <c r="D205" s="15"/>
+      <c r="E205" s="15"/>
+      <c r="F205" s="15"/>
+      <c r="G205" s="6"/>
+      <c r="H205" s="6"/>
+    </row>
+    <row r="206" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="180">
-    <mergeCell ref="B114:B117"/>
-    <mergeCell ref="D114:D117"/>
-    <mergeCell ref="F54:F57"/>
+  <mergeCells count="306">
     <mergeCell ref="C6:C9"/>
     <mergeCell ref="C62:C65"/>
+    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="D194:D197"/>
+    <mergeCell ref="F134:F137"/>
     <mergeCell ref="E62:E65"/>
-    <mergeCell ref="A114:A117"/>
-    <mergeCell ref="D22:D25"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="F78:F81"/>
-    <mergeCell ref="F118:F121"/>
+    <mergeCell ref="F194:F197"/>
+    <mergeCell ref="A198:A201"/>
+    <mergeCell ref="C198:C201"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="D122:D125"/>
+    <mergeCell ref="A126:A129"/>
+    <mergeCell ref="C130:C133"/>
+    <mergeCell ref="F122:F125"/>
+    <mergeCell ref="D162:D165"/>
+    <mergeCell ref="C182:C185"/>
+    <mergeCell ref="A142:A145"/>
+    <mergeCell ref="E182:E185"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="F106:F109"/>
+    <mergeCell ref="A190:A193"/>
+    <mergeCell ref="C150:C153"/>
+    <mergeCell ref="F186:F189"/>
+    <mergeCell ref="C190:C193"/>
+    <mergeCell ref="B114:B117"/>
+    <mergeCell ref="D74:D77"/>
+    <mergeCell ref="D114:D117"/>
     <mergeCell ref="D6:D9"/>
     <mergeCell ref="C26:C29"/>
+    <mergeCell ref="D190:D193"/>
     <mergeCell ref="B86:B89"/>
+    <mergeCell ref="A138:A141"/>
     <mergeCell ref="E82:E85"/>
     <mergeCell ref="F6:F9"/>
     <mergeCell ref="D86:D89"/>
     <mergeCell ref="F86:F89"/>
+    <mergeCell ref="F142:F145"/>
     <mergeCell ref="C10:C13"/>
     <mergeCell ref="B62:B65"/>
     <mergeCell ref="E10:E13"/>
@@ -2574,101 +4823,167 @@
     <mergeCell ref="E98:E101"/>
     <mergeCell ref="F70:F73"/>
     <mergeCell ref="E34:E37"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="C110:C113"/>
-    <mergeCell ref="F106:F109"/>
-    <mergeCell ref="F114:F117"/>
-    <mergeCell ref="A118:A121"/>
-    <mergeCell ref="C118:C121"/>
-    <mergeCell ref="F26:F29"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="C50:C53"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="E118:E121"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="D66:D69"/>
-    <mergeCell ref="D106:D109"/>
-    <mergeCell ref="F66:F69"/>
-    <mergeCell ref="D18:D21"/>
-    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="B182:B185"/>
+    <mergeCell ref="D134:D137"/>
+    <mergeCell ref="E22:E25"/>
+    <mergeCell ref="B154:B157"/>
+    <mergeCell ref="C174:C177"/>
+    <mergeCell ref="C194:C197"/>
+    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="D58:D61"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="F58:F61"/>
+    <mergeCell ref="A122:A125"/>
+    <mergeCell ref="C122:C125"/>
+    <mergeCell ref="A202:A205"/>
+    <mergeCell ref="C78:C81"/>
+    <mergeCell ref="D42:D45"/>
+    <mergeCell ref="A186:A189"/>
+    <mergeCell ref="C186:C189"/>
+    <mergeCell ref="D94:D97"/>
+    <mergeCell ref="E142:E145"/>
+    <mergeCell ref="E194:E197"/>
+    <mergeCell ref="B150:B153"/>
+    <mergeCell ref="A114:A117"/>
+    <mergeCell ref="A170:A173"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="C170:C173"/>
+    <mergeCell ref="F78:F81"/>
+    <mergeCell ref="F118:F121"/>
+    <mergeCell ref="F158:F161"/>
+    <mergeCell ref="B190:B193"/>
+    <mergeCell ref="B178:B181"/>
     <mergeCell ref="E86:E89"/>
     <mergeCell ref="B34:B37"/>
     <mergeCell ref="A42:A45"/>
     <mergeCell ref="F38:F41"/>
     <mergeCell ref="F50:F53"/>
     <mergeCell ref="B74:B77"/>
+    <mergeCell ref="D130:D133"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="E162:E165"/>
+    <mergeCell ref="F130:F133"/>
+    <mergeCell ref="A134:A137"/>
+    <mergeCell ref="B162:B165"/>
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="F170:F173"/>
+    <mergeCell ref="B138:B141"/>
+    <mergeCell ref="E134:E137"/>
+    <mergeCell ref="D138:D141"/>
+    <mergeCell ref="F54:F57"/>
+    <mergeCell ref="C158:C161"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="D66:D69"/>
+    <mergeCell ref="D106:D109"/>
+    <mergeCell ref="F66:F69"/>
+    <mergeCell ref="B146:B149"/>
+    <mergeCell ref="D18:D21"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="E166:E169"/>
+    <mergeCell ref="B202:B205"/>
+    <mergeCell ref="F166:F169"/>
+    <mergeCell ref="E198:E201"/>
+    <mergeCell ref="C74:C77"/>
+    <mergeCell ref="A110:A113"/>
+    <mergeCell ref="F162:F165"/>
+    <mergeCell ref="C126:C129"/>
+    <mergeCell ref="E126:E129"/>
+    <mergeCell ref="C166:C169"/>
+    <mergeCell ref="B94:B97"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="E138:E141"/>
+    <mergeCell ref="E190:E193"/>
+    <mergeCell ref="D158:D161"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="F114:F117"/>
+    <mergeCell ref="D154:D157"/>
+    <mergeCell ref="A118:A121"/>
+    <mergeCell ref="C118:C121"/>
+    <mergeCell ref="A158:A161"/>
+    <mergeCell ref="F154:F157"/>
+    <mergeCell ref="D186:D189"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="B174:B177"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="B126:B129"/>
+    <mergeCell ref="D182:D185"/>
+    <mergeCell ref="D38:D41"/>
+    <mergeCell ref="F182:F185"/>
+    <mergeCell ref="A130:A133"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="E106:E109"/>
+    <mergeCell ref="B54:B57"/>
     <mergeCell ref="D110:D113"/>
+    <mergeCell ref="E146:E149"/>
     <mergeCell ref="A58:A61"/>
-    <mergeCell ref="C74:C77"/>
-    <mergeCell ref="B94:B97"/>
-    <mergeCell ref="A110:A113"/>
     <mergeCell ref="C58:C61"/>
     <mergeCell ref="E58:E61"/>
-    <mergeCell ref="D90:D93"/>
     <mergeCell ref="B46:B49"/>
-    <mergeCell ref="B102:B105"/>
     <mergeCell ref="A66:A69"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="D58:D61"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="C78:C81"/>
-    <mergeCell ref="D94:D97"/>
-    <mergeCell ref="D74:D77"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="C22:C25"/>
-    <mergeCell ref="F18:F21"/>
-    <mergeCell ref="E78:E81"/>
+    <mergeCell ref="F26:F29"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="C50:C53"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="F138:F141"/>
+    <mergeCell ref="E202:E205"/>
+    <mergeCell ref="A174:A177"/>
+    <mergeCell ref="D170:D173"/>
     <mergeCell ref="B58:B61"/>
     <mergeCell ref="F2:F5"/>
     <mergeCell ref="E6:E9"/>
+    <mergeCell ref="C134:C137"/>
+    <mergeCell ref="E186:E189"/>
     <mergeCell ref="F22:F25"/>
+    <mergeCell ref="A154:A157"/>
+    <mergeCell ref="C114:C117"/>
     <mergeCell ref="E30:E33"/>
+    <mergeCell ref="E170:E173"/>
     <mergeCell ref="C70:C73"/>
+    <mergeCell ref="E114:E117"/>
     <mergeCell ref="E70:E73"/>
+    <mergeCell ref="F102:F105"/>
     <mergeCell ref="C46:C49"/>
+    <mergeCell ref="C106:C109"/>
+    <mergeCell ref="A194:A197"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="F190:F193"/>
     <mergeCell ref="B30:B33"/>
-    <mergeCell ref="E54:E57"/>
-    <mergeCell ref="D30:D33"/>
-    <mergeCell ref="D62:D65"/>
-    <mergeCell ref="F62:F65"/>
-    <mergeCell ref="D14:D17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="D38:D41"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="C138:C141"/>
     <mergeCell ref="F10:F13"/>
+    <mergeCell ref="D50:D53"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="F202:F205"/>
     <mergeCell ref="A94:A97"/>
+    <mergeCell ref="F146:F149"/>
+    <mergeCell ref="B122:B125"/>
+    <mergeCell ref="E150:E153"/>
+    <mergeCell ref="D178:D181"/>
     <mergeCell ref="D34:D37"/>
+    <mergeCell ref="F178:F181"/>
+    <mergeCell ref="A182:A185"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="C42:C45"/>
     <mergeCell ref="F34:F37"/>
     <mergeCell ref="A78:A81"/>
     <mergeCell ref="F74:F77"/>
     <mergeCell ref="E42:E45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="F58:F61"/>
-    <mergeCell ref="D42:D45"/>
-    <mergeCell ref="C18:C21"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="E18:E21"/>
-    <mergeCell ref="E22:E25"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="C82:C85"/>
-    <mergeCell ref="D102:D105"/>
+    <mergeCell ref="B106:B109"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="E122:E125"/>
+    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="C202:C205"/>
+    <mergeCell ref="D202:D205"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A150:A153"/>
     <mergeCell ref="E26:E29"/>
     <mergeCell ref="D98:D101"/>
     <mergeCell ref="C66:C69"/>
@@ -2677,56 +4992,97 @@
     <mergeCell ref="C102:C105"/>
     <mergeCell ref="A34:A37"/>
     <mergeCell ref="B26:B29"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="D82:D85"/>
+    <mergeCell ref="E50:E53"/>
+    <mergeCell ref="C86:C89"/>
     <mergeCell ref="D26:D29"/>
-    <mergeCell ref="D82:D85"/>
-    <mergeCell ref="C34:C37"/>
-    <mergeCell ref="C86:C89"/>
-    <mergeCell ref="E50:E53"/>
+    <mergeCell ref="E130:E133"/>
     <mergeCell ref="D54:D57"/>
+    <mergeCell ref="B134:B137"/>
+    <mergeCell ref="B194:B197"/>
     <mergeCell ref="D10:D13"/>
-    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="B170:B173"/>
+    <mergeCell ref="E78:E81"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B158:B161"/>
+    <mergeCell ref="E110:E113"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="B186:B189"/>
+    <mergeCell ref="C82:C85"/>
+    <mergeCell ref="D102:D105"/>
+    <mergeCell ref="B142:B145"/>
+    <mergeCell ref="E174:E177"/>
+    <mergeCell ref="D142:D145"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="C178:C181"/>
+    <mergeCell ref="E54:E57"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="E178:E181"/>
+    <mergeCell ref="D62:D65"/>
+    <mergeCell ref="D118:D121"/>
+    <mergeCell ref="D14:D17"/>
+    <mergeCell ref="A106:A109"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="C142:C145"/>
+    <mergeCell ref="D198:D201"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="A146:A149"/>
+    <mergeCell ref="F198:F201"/>
+    <mergeCell ref="C146:C149"/>
+    <mergeCell ref="D174:D177"/>
+    <mergeCell ref="A178:A181"/>
+    <mergeCell ref="F174:F177"/>
+    <mergeCell ref="D126:D129"/>
+    <mergeCell ref="C94:C97"/>
+    <mergeCell ref="F126:F129"/>
+    <mergeCell ref="D166:D169"/>
+    <mergeCell ref="E94:E97"/>
+    <mergeCell ref="E90:E93"/>
     <mergeCell ref="F110:F113"/>
+    <mergeCell ref="D150:D153"/>
+    <mergeCell ref="F150:F153"/>
+    <mergeCell ref="E158:E161"/>
+    <mergeCell ref="B166:B169"/>
+    <mergeCell ref="B118:B121"/>
+    <mergeCell ref="F94:F97"/>
+    <mergeCell ref="E154:E157"/>
+    <mergeCell ref="F98:F101"/>
+    <mergeCell ref="B198:B201"/>
+    <mergeCell ref="F30:F33"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="E38:E41"/>
+    <mergeCell ref="C162:C165"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="B130:B133"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="D46:D49"/>
+    <mergeCell ref="C54:C57"/>
+    <mergeCell ref="A74:A77"/>
     <mergeCell ref="B38:B41"/>
-    <mergeCell ref="A98:A101"/>
-    <mergeCell ref="A18:A21"/>
     <mergeCell ref="F46:F49"/>
     <mergeCell ref="E74:E77"/>
     <mergeCell ref="B78:B81"/>
     <mergeCell ref="F42:F45"/>
-    <mergeCell ref="B118:B121"/>
-    <mergeCell ref="E110:E113"/>
-    <mergeCell ref="F94:F97"/>
     <mergeCell ref="D78:D81"/>
-    <mergeCell ref="F98:F101"/>
     <mergeCell ref="F82:F85"/>
-    <mergeCell ref="D50:D53"/>
-    <mergeCell ref="B106:B109"/>
-    <mergeCell ref="C114:C117"/>
-    <mergeCell ref="E114:E117"/>
-    <mergeCell ref="F102:F105"/>
-    <mergeCell ref="C106:C109"/>
-    <mergeCell ref="D118:D121"/>
-    <mergeCell ref="A106:A109"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="E106:E109"/>
+    <mergeCell ref="F62:F65"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="E118:E121"/>
     <mergeCell ref="C14:C17"/>
+    <mergeCell ref="B66:B69"/>
+    <mergeCell ref="C154:C157"/>
     <mergeCell ref="C98:C101"/>
-    <mergeCell ref="B66:B69"/>
     <mergeCell ref="E14:E17"/>
+    <mergeCell ref="A166:A169"/>
     <mergeCell ref="E102:E105"/>
     <mergeCell ref="B50:B53"/>
-    <mergeCell ref="F30:F33"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="E38:E41"/>
-    <mergeCell ref="C30:C33"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="D46:D49"/>
-    <mergeCell ref="C54:C57"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="C94:C97"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="E94:E97"/>
-    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="A162:A165"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A26:A29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
